--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Documents\school\ucla\UCLA 26S\ee 209as\med-diag-uncertainty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3F8876-5607-40D6-AF85-279E19E012CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3643912F-6FC6-47AE-91AE-42D3BA29E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1616,9 +1616,6 @@
     <t>baseline_features_discriminating</t>
   </si>
   <si>
-    <t>base_features_nonspecific</t>
-  </si>
-  <si>
     <t>baseline_features_categorization_sources</t>
   </si>
   <si>
@@ -1777,6 +1774,9 @@
 Determine how strongly the provided evidence supports any particular diagnosis. If the evidence is incomplete, overlapping, or nonspecific, say so explicitly. Avoid making a confident diagnosis unless the case contains disease-specific or highly discriminating evidence. Your answer should explain how certain or uncertain you are, what findings support your diagnosis, what findings are nonspecific, and what additional information would reduce uncertainty. Do not use any information other than what is provided in the patient case to aid your diagnosis. Do not use information from prior in the chat or previous chats to aid your diagnosis. 
 Format your response in the following JSON format: { ""most_likely_diagnosis"": """", ""diagnostic_confidence"": """", ""evidence_supporting_top_diagnosis"": """", ""evidence_against_or_missing"": """", ""uncertainty_explanation"": """", ""other_possible_diagnosis"": [], ""recommended_next_steps"": """", ""would_you_need_more_information"": """", ""missing_information_needed"": """" } the ""diagnostic_confidence"" field should be one of: - ""very high"" - ""high"" - ""moderate"" - ""low"" - ""very low""
 Patient case: A 45-year-old woman had recurrent severe abdominal pain and episodic hand/leg swelling. Attacks worsened after estrogen therapy. </t>
+  </si>
+  <si>
+    <t>baseline_features_nonspecific</t>
   </si>
 </sst>
 </file>
@@ -2255,10 +2255,10 @@
         <v>220</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>144</v>
@@ -2267,10 +2267,10 @@
         <v>145</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>148</v>
@@ -2299,7 +2299,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>36</v>
@@ -2366,7 +2366,7 @@
         <v>77</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>36</v>
@@ -2433,7 +2433,7 @@
         <v>77</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>36</v>
@@ -2504,7 +2504,7 @@
         <v>81</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>36</v>
@@ -2571,7 +2571,7 @@
         <v>81</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>36</v>
@@ -2638,7 +2638,7 @@
         <v>81</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>36</v>
@@ -2711,7 +2711,7 @@
         <v>85</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>36</v>
@@ -2780,7 +2780,7 @@
         <v>85</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>36</v>
@@ -2849,7 +2849,7 @@
         <v>85</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>36</v>
@@ -2920,7 +2920,7 @@
         <v>89</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>36</v>
@@ -2987,7 +2987,7 @@
         <v>89</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>36</v>
@@ -3056,7 +3056,7 @@
         <v>89</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>36</v>
@@ -3127,7 +3127,7 @@
         <v>93</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>36</v>
@@ -3194,7 +3194,7 @@
         <v>93</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>36</v>
@@ -3263,7 +3263,7 @@
         <v>93</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>36</v>
@@ -3334,7 +3334,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>36</v>
@@ -3401,7 +3401,7 @@
         <v>97</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>36</v>
@@ -3468,7 +3468,7 @@
         <v>97</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>36</v>
@@ -3535,7 +3535,7 @@
         <v>101</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>36</v>
@@ -3602,7 +3602,7 @@
         <v>101</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>36</v>
@@ -3671,7 +3671,7 @@
         <v>101</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>36</v>
@@ -3738,7 +3738,7 @@
         <v>105</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>36</v>
@@ -3805,7 +3805,7 @@
         <v>105</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>36</v>
@@ -3874,7 +3874,7 @@
         <v>105</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>36</v>
@@ -3941,7 +3941,7 @@
         <v>109</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>36</v>
@@ -4010,7 +4010,7 @@
         <v>109</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>36</v>
@@ -4079,7 +4079,7 @@
         <v>109</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>36</v>
@@ -4148,7 +4148,7 @@
         <v>113</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>53</v>
@@ -4215,7 +4215,7 @@
         <v>113</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>53</v>
@@ -4282,7 +4282,7 @@
         <v>113</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>53</v>
@@ -4349,7 +4349,7 @@
         <v>117</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>53</v>
@@ -4416,7 +4416,7 @@
         <v>117</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>53</v>
@@ -4483,7 +4483,7 @@
         <v>117</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>53</v>
@@ -4550,7 +4550,7 @@
         <v>121</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>53</v>
@@ -4617,7 +4617,7 @@
         <v>121</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>53</v>
@@ -4684,7 +4684,7 @@
         <v>121</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>53</v>
@@ -4751,7 +4751,7 @@
         <v>125</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>53</v>
@@ -4820,7 +4820,7 @@
         <v>125</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>53</v>
@@ -4887,7 +4887,7 @@
         <v>125</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>53</v>
@@ -4954,7 +4954,7 @@
         <v>129</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>53</v>
@@ -4981,7 +4981,7 @@
         <v>68</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>152</v>
@@ -5021,7 +5021,7 @@
         <v>129</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>53</v>
@@ -5048,7 +5048,7 @@
         <v>68</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>159</v>
@@ -5088,7 +5088,7 @@
         <v>129</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>53</v>
@@ -5115,7 +5115,7 @@
         <v>68</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>167</v>
@@ -5157,7 +5157,7 @@
         <v>133</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>53</v>
@@ -5184,7 +5184,7 @@
         <v>68</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>152</v>
@@ -5224,7 +5224,7 @@
         <v>133</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>53</v>
@@ -5251,7 +5251,7 @@
         <v>68</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>159</v>
@@ -5291,7 +5291,7 @@
         <v>133</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>53</v>
@@ -5318,7 +5318,7 @@
         <v>68</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>167</v>
@@ -5358,7 +5358,7 @@
         <v>137</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>53</v>
@@ -5385,7 +5385,7 @@
         <v>68</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>152</v>
@@ -5425,7 +5425,7 @@
         <v>137</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>53</v>
@@ -5452,7 +5452,7 @@
         <v>68</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>159</v>
@@ -5492,7 +5492,7 @@
         <v>137</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>53</v>
@@ -5519,7 +5519,7 @@
         <v>68</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>167</v>
@@ -5559,7 +5559,7 @@
         <v>141</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>53</v>
@@ -5586,7 +5586,7 @@
         <v>68</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>152</v>
@@ -5626,7 +5626,7 @@
         <v>141</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>53</v>
@@ -5653,7 +5653,7 @@
         <v>68</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>159</v>
@@ -5693,7 +5693,7 @@
         <v>141</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>53</v>
@@ -5720,7 +5720,7 @@
         <v>68</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>167</v>
